--- a/OCT_2026/10-22-26/Jabbar.xlsx
+++ b/OCT_2026/10-22-26/Jabbar.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D380F1-166C-4864-AA18-F7DC1C34770A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F08101-B48F-45A5-A007-BB13756AFF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="948" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -47854,7 +47854,7 @@
       <c r="L4" s="371"/>
       <c r="M4" s="401">
         <f ca="1">TODAY()+1</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="N4" s="401"/>
       <c r="O4" s="401"/>
@@ -47882,7 +47882,7 @@
       <c r="L5" s="371"/>
       <c r="M5" s="401">
         <f ca="1">M4-1</f>
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="N5" s="370"/>
       <c r="O5" s="370"/>
@@ -54182,7 +54182,7 @@
       </c>
       <c r="T5" s="301">
         <f>+'3'!P35</f>
-        <v>6272.4231701694916</v>
+        <v>6097.2154901694912</v>
       </c>
       <c r="XEX5" t="s">
         <v>106</v>
@@ -54528,7 +54528,7 @@
       </c>
       <c r="J10" s="286">
         <f>+'1'!J19+'2'!J19+'3'!J19+'4'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19+'19'!J19+'20'!J19+'21'!J19+'22'!J19+'23'!J19+'24'!J19+'25'!J19+'26'!J19+'27'!J19+'28'!J19+'29'!J19+'30'!J19</f>
-        <v>366.10560000000004</v>
+        <v>453.27360000000004</v>
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
@@ -54540,7 +54540,7 @@
       </c>
       <c r="M10" s="230">
         <f t="shared" si="1"/>
-        <v>4050.0431999999996</v>
+        <v>3962.8751999999995</v>
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
@@ -54548,11 +54548,11 @@
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>24.574792271186443</v>
+        <v>24.13895227118644</v>
       </c>
       <c r="P10" s="311">
         <f t="shared" si="2"/>
-        <v>4939.5332465084739</v>
+        <v>4851.9294065084741</v>
       </c>
       <c r="Q10" s="213">
         <f>+'1'!Q19+'2'!Q19+'3'!Q19+'4'!Q19+'5'!Q19+'6'!Q19+'7'!Q19+'8'!Q19+'9'!Q19+'10'!Q19+'11'!Q19+'12'!Q19+'13'!Q19+'14'!Q19+'15'!Q19+'16'!Q19+'17'!Q19+'18'!Q19+'19'!Q19+'20'!Q19+'21'!Q19+'22'!Q19+'23'!Q19+'24'!Q19+'25'!Q19+'26'!Q19+'27'!Q19+'28'!Q19+'29'!Q19+'30'!Q19</f>
@@ -54688,7 +54688,7 @@
       </c>
       <c r="J12" s="286">
         <f>+'1'!J21+'2'!J21+'3'!J21+'4'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21+'19'!J21+'20'!J21+'21'!J21+'22'!J21+'23'!J21+'24'!J21+'25'!J21+'26'!J21+'27'!J21+'28'!J21+'29'!J21+'30'!J21</f>
-        <v>511.38560000000001</v>
+        <v>598.55359999999996</v>
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
@@ -54700,7 +54700,7 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>5657.2031999999999</v>
+        <v>5570.0351999999993</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
@@ -54708,11 +54708,11 @@
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>34.326693966101701</v>
+        <v>33.890853966101695</v>
       </c>
       <c r="P12" s="311">
         <f t="shared" si="2"/>
-        <v>6899.6654871864403</v>
+        <v>6812.0616471864405</v>
       </c>
       <c r="Q12" s="213">
         <f>+'1'!Q21+'2'!Q21+'3'!Q21+'4'!Q21+'5'!Q21+'6'!Q21+'7'!Q21+'8'!Q21+'9'!Q21+'10'!Q21+'11'!Q21+'12'!Q21+'13'!Q21+'14'!Q21+'15'!Q21+'16'!Q21+'17'!Q21+'18'!Q21+'19'!Q21+'20'!Q21+'21'!Q21+'22'!Q21+'23'!Q21+'24'!Q21+'25'!Q21+'26'!Q21+'27'!Q21+'28'!Q21+'29'!Q21+'30'!Q21</f>
@@ -54996,7 +54996,7 @@
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>1111.8768</v>
+        <v>1286.2128</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
@@ -55008,7 +55008,7 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>12300.1371</v>
+        <v>12125.801099999999</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
@@ -55016,11 +55016,11 @@
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>74.634583805084759</v>
+        <v>73.762903805084747</v>
       </c>
       <c r="P16" s="113">
         <f>SUM(P7:P15)</f>
-        <v>15001.551344822034</v>
+        <v>14826.343664822034</v>
       </c>
       <c r="Q16" s="128">
         <f>SUM(Q7:Q15)</f>
@@ -55139,7 +55139,7 @@
       <c r="O20" s="387"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>1111.8768</v>
+        <v>1286.2128</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -55204,7 +55204,7 @@
       <c r="O22" s="387"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>12300.1371</v>
+        <v>12125.801100000001</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -55272,7 +55272,7 @@
       <c r="O24" s="389"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>14926.91676101695</v>
+        <v>14752.58076101695</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -55308,7 +55308,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>74.634583805084759</v>
+        <v>73.762903805084747</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -55329,7 +55329,7 @@
       <c r="O26" s="346"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>15001.551344822035</v>
+        <v>14826.343664822036</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -55443,7 +55443,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>15001.551344822034</v>
+        <v>14826.343664822034</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -58346,7 +58346,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -58826,7 +58826,7 @@
       </c>
       <c r="Q16" s="318"/>
       <c r="S16" s="269">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="T16" s="270">
         <v>3.5000000000000003E-2</v>
@@ -58901,7 +58901,7 @@
       <c r="Q17" s="319"/>
       <c r="S17" s="269">
         <f>+S16</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="T17" s="270">
         <f>+T16</f>
@@ -58977,7 +58977,7 @@
       <c r="Q18" s="319"/>
       <c r="S18" s="269">
         <f>+S17</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="T18" s="270">
         <f>+T17</f>
@@ -59023,7 +59023,7 @@
       </c>
       <c r="J19" s="272">
         <f t="shared" si="1"/>
-        <v>232.44800000000001</v>
+        <v>319.61599999999999</v>
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
@@ -59035,7 +59035,7 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2571.4560000000001</v>
+        <v>2484.288</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
@@ -59043,16 +59043,16 @@
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>15.603042711864408</v>
+        <v>15.167202711864407</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>3136.2115850847458</v>
+        <v>3048.6077450847456</v>
       </c>
       <c r="Q19" s="319"/>
       <c r="S19" s="269">
         <f>+S18</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="T19" s="270">
         <v>3.5000000000000003E-2</v>
@@ -59124,7 +59124,7 @@
       <c r="Q20" s="319"/>
       <c r="S20" s="269">
         <f>+S19</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="T20" s="270">
         <f>+T19</f>
@@ -59170,7 +59170,7 @@
       </c>
       <c r="J21" s="272">
         <f t="shared" si="1"/>
-        <v>232.44800000000001</v>
+        <v>319.61599999999999</v>
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
@@ -59182,7 +59182,7 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>2571.4560000000001</v>
+        <v>2484.288</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
@@ -59190,16 +59190,16 @@
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>15.603042711864408</v>
+        <v>15.167202711864407</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>3136.2115850847458</v>
+        <v>3048.6077450847456</v>
       </c>
       <c r="Q21" s="319"/>
       <c r="S21" s="269">
         <f>+S20</f>
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="T21" s="270">
         <f>+T20</f>
@@ -59460,7 +59460,7 @@
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>464.89600000000002</v>
+        <v>639.23199999999997</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
@@ -59472,7 +59472,7 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>5142.9120000000003</v>
+        <v>4968.576</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
@@ -59480,11 +59480,11 @@
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>31.206085423728815</v>
+        <v>30.334405423728814</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>6272.4231701694916</v>
+        <v>6097.2154901694912</v>
       </c>
       <c r="Q25" s="239">
         <f>SUM(Q16:Q24)</f>
@@ -59559,7 +59559,7 @@
       <c r="O29" s="387"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>464.89600000000002</v>
+        <v>639.23199999999997</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59602,7 +59602,7 @@
       <c r="O31" s="387"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>5142.9120000000003</v>
+        <v>4968.576</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59648,7 +59648,7 @@
       <c r="O33" s="389"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>6241.2170847457628</v>
+        <v>6066.8810847457626</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59673,7 +59673,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>31.206085423728815</v>
+        <v>30.334405423728814</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59683,7 +59683,7 @@
       <c r="O35" s="346"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>6272.4231701694916</v>
+        <v>6097.2154901694912</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -59770,7 +59770,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -61192,7 +61192,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -62618,7 +62618,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
